--- a/docs/03-项目分工计划表.xlsx
+++ b/docs/03-项目分工计划表.xlsx
@@ -881,7 +881,7 @@
       </c>
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P7</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P9</t>
         </is>
       </c>
       <c r="C43" s="19" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="B47" s="35" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -4560,7 +4560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="B5" s="28" t="inlineStr">
         <is>
-          <t>B人才档案(后端)</t>
+          <t>B人才档案(后端)+G知识库</t>
         </is>
       </c>
       <c r="C5" s="28" t="inlineStr">
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="D5" s="27" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" s="27" t="n">
         <v>0</v>
@@ -4696,7 +4696,7 @@
         <v>7</v>
       </c>
       <c r="I5" s="27" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B9" s="36" t="inlineStr">
         <is>
-          <t>D岗位匹配(后端)</t>
+          <t>D岗位匹配(后端)+AI基建</t>
         </is>
       </c>
       <c r="C9" s="36" t="inlineStr">
@@ -4833,10 +4833,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I9" s="35" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D岗位匹配(前端)</t>
+          <t>D岗位匹配(前端)+J01-J04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4862,7 +4862,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G10" s="38" t="n">
         <v>9</v>
@@ -4871,7 +4871,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="38" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>E智能培训(前端)</t>
+          <t>E智能培训(前端)+J05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4932,7 +4932,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G12" t="n">
         <v>9</v>
@@ -4941,7 +4941,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>F数据决策(前端)+AI助手</t>
+          <t>F数据决策(前端)+消息/审计页+J06-J07</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
@@ -4999,10 +4999,10 @@
         <v>4</v>
       </c>
       <c r="E14" s="25" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -5011,7 +5011,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>J移动端全量(小程序)</t>
+          <t>J移动端核心(J03/J04/J08)</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
@@ -5037,7 +5037,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="B16" s="29" t="inlineStr">
         <is>
-          <t>H消息+I审计+G知识库+QA</t>
+          <t>H消息+I审计+QA回归+部署</t>
         </is>
       </c>
       <c r="C16" s="29" t="inlineStr">
@@ -5066,10 +5066,10 @@
         </is>
       </c>
       <c r="D16" s="29" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F16" s="29" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I16" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="B25" s="39" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C25" s="39" t="n">
         <v>0</v>
@@ -5224,7 +5224,7 @@
         <v>7</v>
       </c>
       <c r="E25" s="39" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F25" s="39" t="inlineStr">
         <is>
@@ -5320,10 +5320,10 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C30" t="n">
         <v>9</v>
@@ -5347,7 +5347,7 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C32" t="n">
         <v>9</v>
@@ -5395,7 +5395,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -5482,16 +5482,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E36" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5499,6 +5499,11 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/03-项目分工计划表.xlsx
+++ b/docs/03-项目分工计划表.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -725,6 +725,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>小组</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -802,6 +807,11 @@
           <t>全员参与</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
@@ -872,6 +882,11 @@
           <t>含 Git 工作流约定</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="35" t="inlineStr">
@@ -881,7 +896,7 @@
       </c>
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P6 林叔宝</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -942,6 +957,11 @@
           <t>原属 P6「从零搭建」，已由底座封装完成，改为 P6 牵头维护，不占 P6 开发工时</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>组3-岗位匹配域</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -958,7 +978,7 @@
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P13 匡子怡</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1015,6 +1035,11 @@
         </is>
       </c>
       <c r="N7" s="10" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
@@ -1024,7 +1049,7 @@
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P13 匡子怡</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1081,6 +1106,11 @@
         </is>
       </c>
       <c r="N8" s="10" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
@@ -1090,7 +1120,7 @@
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P13 匡子怡</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1147,6 +1177,11 @@
         </is>
       </c>
       <c r="N9" s="10" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
@@ -1156,7 +1191,7 @@
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P13 匡子怡</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1213,6 +1248,11 @@
         </is>
       </c>
       <c r="N10" s="10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
@@ -1222,7 +1262,7 @@
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1 董任进</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1283,6 +1323,11 @@
           <t>P1 兼任，贯穿三日</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="27" t="inlineStr">
@@ -1292,7 +1337,7 @@
       </c>
       <c r="B12" s="27" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P2 袁文武</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -1349,6 +1394,11 @@
         </is>
       </c>
       <c r="N12" s="13" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="27" t="inlineStr">
@@ -1358,7 +1408,7 @@
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P2 袁文武</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -1419,6 +1469,11 @@
           <t>复用 AI基建 Milvus</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="27" t="inlineStr">
@@ -1428,7 +1483,7 @@
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P2 袁文武</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
@@ -1489,6 +1544,11 @@
           <t>复用 RAG 工具</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="27" t="inlineStr">
@@ -1498,7 +1558,7 @@
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P3 惠倩</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
@@ -1555,6 +1615,11 @@
         </is>
       </c>
       <c r="N15" s="13" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="29" t="inlineStr">
@@ -1564,7 +1629,7 @@
       </c>
       <c r="B16" s="29" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P4 郭子琦</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -1621,6 +1686,11 @@
         </is>
       </c>
       <c r="N16" s="15" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>组2-智能测评域</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="29" t="inlineStr">
@@ -1630,7 +1700,7 @@
       </c>
       <c r="B17" s="29" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P4 郭子琦</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -1687,6 +1757,11 @@
         </is>
       </c>
       <c r="N17" s="15" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>组2-智能测评域</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="29" t="inlineStr">
@@ -1696,7 +1771,7 @@
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P5 王耀毅</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -1753,6 +1828,11 @@
         </is>
       </c>
       <c r="N18" s="15" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>组2-智能测评域</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="31" t="inlineStr">
@@ -1762,7 +1842,7 @@
       </c>
       <c r="B19" s="31" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P6 林叔宝</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
@@ -1823,6 +1903,11 @@
           <t>复用 Milvus</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>组3-岗位匹配域</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="31" t="inlineStr">
@@ -1832,7 +1917,7 @@
       </c>
       <c r="B20" s="31" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P6 林叔宝</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
@@ -1889,6 +1974,11 @@
         </is>
       </c>
       <c r="N20" s="17" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>组3-岗位匹配域</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="31" t="inlineStr">
@@ -1898,7 +1988,7 @@
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P7 耿龙</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
@@ -1955,6 +2045,11 @@
         </is>
       </c>
       <c r="N21" s="17" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>组3-岗位匹配域</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="31" t="inlineStr">
@@ -1964,7 +2059,7 @@
       </c>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P7 耿龙</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
@@ -2021,6 +2116,11 @@
         </is>
       </c>
       <c r="N22" s="17" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>组3-岗位匹配域</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="33" t="inlineStr">
@@ -2030,7 +2130,7 @@
       </c>
       <c r="B23" s="33" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P8 林恩壕</t>
         </is>
       </c>
       <c r="C23" s="19" t="inlineStr">
@@ -2087,6 +2187,11 @@
         </is>
       </c>
       <c r="N23" s="19" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>组4-智能培训域</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="33" t="inlineStr">
@@ -2096,7 +2201,7 @@
       </c>
       <c r="B24" s="33" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P8 林恩壕</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
@@ -2153,6 +2258,11 @@
         </is>
       </c>
       <c r="N24" s="19" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>组4-智能培训域</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="33" t="inlineStr">
@@ -2162,7 +2272,7 @@
       </c>
       <c r="B25" s="33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P9 何然</t>
         </is>
       </c>
       <c r="C25" s="19" t="inlineStr">
@@ -2219,6 +2329,11 @@
         </is>
       </c>
       <c r="N25" s="19" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>组4-智能培训域</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="35" t="inlineStr">
@@ -2228,7 +2343,7 @@
       </c>
       <c r="B26" s="35" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P10 王泽川</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -2289,6 +2404,11 @@
           <t>AI基建已由底座交付，P6 专注业务开发</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="35" t="inlineStr">
@@ -2298,7 +2418,7 @@
       </c>
       <c r="B27" s="35" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P10 王泽川</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -2355,6 +2475,11 @@
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="35" t="inlineStr">
@@ -2364,7 +2489,7 @@
       </c>
       <c r="B28" s="35" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P11 戈成斌</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -2421,6 +2546,11 @@
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2437,7 +2567,7 @@
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P13 匡子怡</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2494,6 +2624,11 @@
         </is>
       </c>
       <c r="N30" s="10" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="25" t="inlineStr">
@@ -2503,7 +2638,7 @@
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P11 戈成斌</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2560,6 +2695,11 @@
         </is>
       </c>
       <c r="N31" s="10" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="25" t="inlineStr">
@@ -2569,7 +2709,7 @@
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1 董任进+P12 田涌浩</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
@@ -2630,6 +2770,11 @@
           <t>统筹串联 5 个 Agent</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="27" t="inlineStr">
@@ -2639,7 +2784,7 @@
       </c>
       <c r="B33" s="27" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P2 袁文武</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -2696,6 +2841,11 @@
         </is>
       </c>
       <c r="N33" s="13" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="27" t="inlineStr">
@@ -2705,7 +2855,7 @@
       </c>
       <c r="B34" s="27" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P12 田涌浩</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
@@ -2762,6 +2912,11 @@
         </is>
       </c>
       <c r="N34" s="13" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>组2-智能测评域</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="27" t="inlineStr">
@@ -2771,7 +2926,7 @@
       </c>
       <c r="B35" s="27" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P3 惠倩+P2 袁文武</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
@@ -2832,6 +2987,11 @@
           <t>从 0 到 1 闭环，调用 AI基建 LLM/向量</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="29" t="inlineStr">
@@ -2841,7 +3001,7 @@
       </c>
       <c r="B36" s="29" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P4 郭子琦</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
@@ -2898,6 +3058,11 @@
         </is>
       </c>
       <c r="N36" s="15" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>组2-智能测评域</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="29" t="inlineStr">
@@ -2907,7 +3072,7 @@
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P5 王耀毅</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
@@ -2964,6 +3129,11 @@
         </is>
       </c>
       <c r="N37" s="15" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>组2-智能测评域</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="29" t="inlineStr">
@@ -2973,7 +3143,7 @@
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P12 田涌浩</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
@@ -3030,6 +3200,11 @@
         </is>
       </c>
       <c r="N38" s="15" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>组2-智能测评域</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="29" t="inlineStr">
@@ -3039,7 +3214,7 @@
       </c>
       <c r="B39" s="29" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P5 王耀毅+P4 郭子琦</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
@@ -3100,6 +3275,11 @@
           <t>从 0 到 1 闭环</t>
         </is>
       </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>组2-智能测评域</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="31" t="inlineStr">
@@ -3109,7 +3289,7 @@
       </c>
       <c r="B40" s="31" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P12 田涌浩</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
@@ -3166,6 +3346,11 @@
         </is>
       </c>
       <c r="N40" s="17" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>组2-智能测评域</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="31" t="inlineStr">
@@ -3175,7 +3360,7 @@
       </c>
       <c r="B41" s="31" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P9 何然</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
@@ -3232,6 +3417,11 @@
         </is>
       </c>
       <c r="N41" s="17" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>组4-智能培训域</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="31" t="inlineStr">
@@ -3241,7 +3431,7 @@
       </c>
       <c r="B42" s="31" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P7 耿龙+P6 林叔宝</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
@@ -3302,6 +3492,11 @@
           <t>从 0 到 1 闭环</t>
         </is>
       </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>组3-岗位匹配域</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="33" t="inlineStr">
@@ -3311,7 +3506,7 @@
       </c>
       <c r="B43" s="33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P3 惠倩</t>
         </is>
       </c>
       <c r="C43" s="19" t="inlineStr">
@@ -3368,6 +3563,11 @@
         </is>
       </c>
       <c r="N43" s="19" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="33" t="inlineStr">
@@ -3377,7 +3577,7 @@
       </c>
       <c r="B44" s="33" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P9 何然</t>
         </is>
       </c>
       <c r="C44" s="19" t="inlineStr">
@@ -3434,6 +3634,11 @@
         </is>
       </c>
       <c r="N44" s="19" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>组4-智能培训域</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="33" t="inlineStr">
@@ -3443,7 +3648,7 @@
       </c>
       <c r="B45" s="33" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P9 何然+P8 林恩壕</t>
         </is>
       </c>
       <c r="C45" s="19" t="inlineStr">
@@ -3504,6 +3709,11 @@
           <t>从 0 到 1 闭环</t>
         </is>
       </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>组4-智能培训域</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="35" t="inlineStr">
@@ -3513,7 +3723,7 @@
       </c>
       <c r="B46" s="35" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P11 戈成斌</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
@@ -3570,6 +3780,11 @@
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="35" t="inlineStr">
@@ -3579,7 +3794,7 @@
       </c>
       <c r="B47" s="35" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P11 戈成斌</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
@@ -3636,6 +3851,11 @@
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="35" t="inlineStr">
@@ -3645,7 +3865,7 @@
       </c>
       <c r="B48" s="35" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P10 王泽川+P11 戈成斌</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
@@ -3706,6 +3926,11 @@
           <t>从 0 到 1 闭环</t>
         </is>
       </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3722,7 +3947,7 @@
       </c>
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1 董任进+P13 匡子怡</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
@@ -3779,6 +4004,11 @@
         </is>
       </c>
       <c r="N50" s="10" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="27" t="inlineStr">
@@ -3788,7 +4018,7 @@
       </c>
       <c r="B51" s="27" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P2 袁文武</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
@@ -3845,6 +4075,11 @@
         </is>
       </c>
       <c r="N51" s="13" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="29" t="inlineStr">
@@ -3854,7 +4089,7 @@
       </c>
       <c r="B52" s="29" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P4 郭子琦</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
@@ -3911,6 +4146,11 @@
         </is>
       </c>
       <c r="N52" s="15" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>组2-智能测评域</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="31" t="inlineStr">
@@ -3920,7 +4160,7 @@
       </c>
       <c r="B53" s="31" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P6 林叔宝</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
@@ -3977,6 +4217,11 @@
         </is>
       </c>
       <c r="N53" s="17" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>组3-岗位匹配域</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="33" t="inlineStr">
@@ -3986,7 +4231,7 @@
       </c>
       <c r="B54" s="33" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P8 林恩壕</t>
         </is>
       </c>
       <c r="C54" s="19" t="inlineStr">
@@ -4043,6 +4288,11 @@
         </is>
       </c>
       <c r="N54" s="19" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>组4-智能培训域</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="35" t="inlineStr">
@@ -4052,7 +4302,7 @@
       </c>
       <c r="B55" s="35" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P5 王耀毅</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -4113,6 +4363,11 @@
           <t>P6 兼任 QA；AI基建已就绪，回归含工具层验证</t>
         </is>
       </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>组2-智能测评域</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4129,7 +4384,7 @@
       </c>
       <c r="B57" s="25" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1 董任进</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
@@ -4186,6 +4441,11 @@
         </is>
       </c>
       <c r="N57" s="10" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="35" t="inlineStr">
@@ -4195,7 +4455,7 @@
       </c>
       <c r="B58" s="35" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P13 匡子怡</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -4256,6 +4516,11 @@
           <t>P6 牵头（AI基建运维）</t>
         </is>
       </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
@@ -4322,6 +4587,11 @@
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4395,6 +4665,11 @@
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="35" t="inlineStr">
@@ -4404,7 +4679,7 @@
       </c>
       <c r="B62" s="35" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P10 王泽川</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -4465,6 +4740,11 @@
           <t>P6 牵头 AI 演进</t>
         </is>
       </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>组5-数据决策域</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
@@ -4531,6 +4811,11 @@
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>全员</t>
+        </is>
+      </c>
     </row>
     <row r="64"/>
     <row r="65" ht="42" customHeight="1">
@@ -4560,7 +4845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4632,17 +4917,17 @@
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1 董任进</t>
         </is>
       </c>
       <c r="B4" s="26" t="inlineStr">
         <is>
-          <t>项目管理+LangGraph</t>
+          <t>组1·项目统筹+LangGraph</t>
         </is>
       </c>
       <c r="C4" s="26" t="inlineStr">
         <is>
-          <t>协同图设计+串联5Agent</t>
+          <t>协同图+串联5Agent</t>
         </is>
       </c>
       <c r="D4" s="25" t="n">
@@ -4655,29 +4940,29 @@
         <v>0</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H4" s="25" t="n">
         <v>11</v>
       </c>
       <c r="I4" s="25" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="27" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P2 袁文武</t>
         </is>
       </c>
       <c r="B5" s="28" t="inlineStr">
         <is>
-          <t>B人才档案(后端)+G知识库</t>
+          <t>组1·档案后端+知识库</t>
         </is>
       </c>
       <c r="C5" s="28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>①简历解析(协作)</t>
         </is>
       </c>
       <c r="D5" s="27" t="n">
@@ -4690,29 +4975,29 @@
         <v>0</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>7</v>
       </c>
       <c r="I5" s="27" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P3 惠倩</t>
         </is>
       </c>
       <c r="B6" s="30" t="inlineStr">
         <is>
-          <t>B人才档案(前端)</t>
+          <t>组1·档案前端</t>
         </is>
       </c>
       <c r="C6" s="30" t="inlineStr">
         <is>
-          <t>① 简历智能解析</t>
+          <t>①简历解析(主)</t>
         </is>
       </c>
       <c r="D6" s="29" t="n">
@@ -4722,32 +5007,32 @@
         <v>4</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P4 郭子琦</t>
         </is>
       </c>
       <c r="B7" s="32" t="inlineStr">
         <is>
-          <t>C智能测评(后端)</t>
+          <t>组2·测评后端</t>
         </is>
       </c>
       <c r="C7" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>②测评报告(协作)</t>
         </is>
       </c>
       <c r="D7" s="31" t="n">
@@ -4760,29 +5045,29 @@
         <v>0</v>
       </c>
       <c r="G7" s="31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="31" t="n">
         <v>7</v>
       </c>
       <c r="I7" s="31" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="33" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P5 王耀毅</t>
         </is>
       </c>
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>C智能测评(前端)</t>
+          <t>组2·测评前端+QA</t>
         </is>
       </c>
       <c r="C8" s="34" t="inlineStr">
         <is>
-          <t>② 测评分析报告</t>
+          <t>②测评报告(主)</t>
         </is>
       </c>
       <c r="D8" s="33" t="n">
@@ -4795,29 +5080,29 @@
         <v>0</v>
       </c>
       <c r="G8" s="33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H8" s="33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I8" s="33" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P6 林叔宝</t>
         </is>
       </c>
       <c r="B9" s="36" t="inlineStr">
         <is>
-          <t>D岗位匹配(后端)+AI基建</t>
+          <t>组3·匹配后端+AI基建</t>
         </is>
       </c>
       <c r="C9" s="36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>③双向匹配(协作)</t>
         </is>
       </c>
       <c r="D9" s="35" t="n">
@@ -4830,29 +5115,29 @@
         <v>0</v>
       </c>
       <c r="G9" s="35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="35" t="n">
         <v>10</v>
       </c>
       <c r="I9" s="35" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="37" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P7 耿龙</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D岗位匹配(前端)+J01-J04</t>
+          <t>组3·匹配前端+J01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>③ 人才-岗位双向匹配</t>
+          <t>③双向匹配(主)</t>
         </is>
       </c>
       <c r="D10" s="38" t="n">
@@ -4862,32 +5147,32 @@
         <v>3</v>
       </c>
       <c r="F10" s="38" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H10" s="38" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="38" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P8 林恩壕</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>E智能培训(后端)</t>
+          <t>组4·培训后端</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>④培训推送(协作)</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -4900,29 +5185,29 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
         <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P9 何然</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>E智能培训(前端)+J05</t>
+          <t>组4·培训前端+J05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>④ 个性化培训推送</t>
+          <t>④培训推送(主)</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -4932,32 +5217,32 @@
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P10 王泽川</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>F数据决策(后端)</t>
+          <t>组5·决策后端</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>⑤ NL2SQL自由问数</t>
+          <t>⑤NL2SQL(主)</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
@@ -4970,64 +5255,64 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
         <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P11 戈成斌</t>
         </is>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>F数据决策(前端)+消息/审计页+J06-J07</t>
+          <t>组5·决策前端+AI助手</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⑤NL2SQL(协作)</t>
         </is>
       </c>
       <c r="D14" s="25" t="n">
         <v>4</v>
       </c>
       <c r="E14" s="25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F14" s="25" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P12 田涌浩</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>J移动端核心(J03/J04/J08)</t>
+          <t>组2·移动端(J03/J04)</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LangGraph(协作)</t>
         </is>
       </c>
       <c r="D15" s="27" t="n">
@@ -5037,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -5052,33 +5337,33 @@
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P13 匡子怡</t>
         </is>
       </c>
       <c r="B16" s="29" t="inlineStr">
         <is>
-          <t>H消息+I审计+QA回归+部署</t>
+          <t>组5·知识库+消息/审计+QA</t>
         </is>
       </c>
       <c r="C16" s="29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LangGraph QA</t>
         </is>
       </c>
       <c r="D16" s="29" t="n">
         <v>12</v>
       </c>
       <c r="E16" s="29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F16" s="29" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>24</v>
@@ -5102,13 +5387,13 @@
         <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H17" t="n">
         <v>60</v>
       </c>
       <c r="I17" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18">
@@ -5127,7 +5412,6 @@
       <c r="E19" s="35" t="n"/>
       <c r="F19" s="35" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
         <is>
@@ -5184,20 +5468,20 @@
     <row r="24">
       <c r="A24" s="39" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P1 董任进</t>
         </is>
       </c>
       <c r="B24" s="39" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="39" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D24" s="39" t="n">
         <v>11</v>
       </c>
       <c r="E24" s="39" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F24" s="39" t="inlineStr">
         <is>
@@ -5211,20 +5495,20 @@
     <row r="25">
       <c r="A25" s="39" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P2 袁文武</t>
         </is>
       </c>
       <c r="B25" s="39" t="n">
         <v>17</v>
       </c>
       <c r="C25" s="39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D25" s="39" t="n">
         <v>7</v>
       </c>
       <c r="E25" s="39" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F25" s="39" t="inlineStr">
         <is>
@@ -5238,20 +5522,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P3 惠倩</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -5262,20 +5546,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P4 郭子琦</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>12</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
         <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -5286,20 +5570,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P5 王耀毅</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -5310,20 +5594,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>P6</t>
+          <t>P6 林叔宝</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
         <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -5334,20 +5618,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>P7</t>
+          <t>P7 耿龙</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -5358,20 +5642,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>P8</t>
+          <t>P8 林恩壕</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
         <v>7</v>
       </c>
       <c r="E31" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -5382,20 +5666,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>P9</t>
+          <t>P9 何然</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -5406,20 +5690,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>P10</t>
+          <t>P10 王泽川</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>9</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
         <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -5430,20 +5714,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P11 戈成斌</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5454,14 +5738,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P12 田涌浩</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -5478,17 +5762,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>P13</t>
+          <t>P13 匡子怡</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
         <v>24</v>
@@ -5499,11 +5783,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/03-项目分工计划表.xlsx
+++ b/docs/03-项目分工计划表.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -228,8 +228,12 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="46">
+  <fills count="48">
     <fill>
       <patternFill/>
     </fill>
@@ -500,8 +504,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF5FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -666,6 +680,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
@@ -814,7 +834,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -913,6 +933,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="46" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="47" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1325,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1660,70 +1686,70 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>T-A-01</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>P1 董任进</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="36" t="inlineStr">
         <is>
           <t>A系统权限</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>认证/RBAC/用户/角色/菜单/部门/字典 后端</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>后端</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>JWT认证+RBAC权限模型+用户/角色/菜单/部门/字典 CRUD 接口</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="36" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="36" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="36" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" s="36" t="inlineStr">
         <is>
           <t>底座就绪</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M7" s="36" t="inlineStr">
         <is>
           <t>系统权限域接口全部可用</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="36" t="inlineStr">
         <is>
           <t>P1 牵头完成并上传 Git</t>
         </is>
@@ -1735,70 +1761,70 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>T-A-02</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>P1 董任进</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="36" t="inlineStr">
         <is>
           <t>A系统权限</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>管理端系统管理域 9 页面 (管理端)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>前端-管理端</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>用户/角色/菜单/部门/字典/操作日志/登录日志/消息中心页面+动态路由</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="36" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="36" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="36" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" s="36" t="inlineStr">
         <is>
           <t>T-A-01</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M8" s="36" t="inlineStr">
         <is>
           <t>管理端 9 页面可操作、动态路由生效</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" s="36" t="inlineStr">
         <is>
           <t>P1 牵头完成并上传 Git</t>
         </is>
@@ -1810,70 +1836,70 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>T-A-03</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>P1 董任进</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="36" t="inlineStr">
         <is>
           <t>A系统权限</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>全局响应/异常/日志/Alembic迁移/云端库</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>后端</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>统一响应+5类异常处理+统一日志+Alembic迁移+云端MySQL配置</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="36" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="36" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="36" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="36" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" s="36" t="inlineStr">
         <is>
           <t>底座就绪</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M9" s="36" t="inlineStr">
         <is>
           <t>基建全链路可用</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N9" s="36" t="inlineStr">
         <is>
           <t>P1 牵头完成并上传 Git</t>
         </is>
@@ -5493,9 +5519,309 @@
         </is>
       </c>
     </row>
-    <row r="67"/>
+    <row r="67">
+      <c r="A67" s="37" t="inlineStr">
+        <is>
+          <t>T-P1-10</t>
+        </is>
+      </c>
+      <c r="B67" s="37" t="inlineStr">
+        <is>
+          <t>P1 董任进</t>
+        </is>
+      </c>
+      <c r="C67" s="37" t="inlineStr">
+        <is>
+          <t>项目管理</t>
+        </is>
+      </c>
+      <c r="D67" s="37" t="inlineStr">
+        <is>
+          <t>基座缺陷修复（14 个 Bug）</t>
+        </is>
+      </c>
+      <c r="E67" s="37" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="F67" s="37" t="inlineStr">
+        <is>
+          <t>jose包冲突/sys.path/.env路径/登录无反应/侧边栏空白/RBAC权限/刷新丢菜单等 14 个 Bug 定位与修复</t>
+        </is>
+      </c>
+      <c r="G67" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H67" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="I67" s="37" t="n">
+        <v>8</v>
+      </c>
+      <c r="J67" s="37" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="K67" s="37" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L67" s="37" t="inlineStr">
+        <is>
+          <t>T-A-01~03</t>
+        </is>
+      </c>
+      <c r="M67" s="37" t="inlineStr">
+        <is>
+          <t>14 个 Bug 全部修复并回归通过</t>
+        </is>
+      </c>
+      <c r="N67" s="37" t="inlineStr">
+        <is>
+          <t>全部已提交 Git</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="33" t="inlineStr">
+      <c r="A68" s="37" t="inlineStr">
+        <is>
+          <t>T-P1-11</t>
+        </is>
+      </c>
+      <c r="B68" s="37" t="inlineStr">
+        <is>
+          <t>P1 董任进</t>
+        </is>
+      </c>
+      <c r="C68" s="37" t="inlineStr">
+        <is>
+          <t>项目管理</t>
+        </is>
+      </c>
+      <c r="D68" s="37" t="inlineStr">
+        <is>
+          <t>技术文档（使用手册+Bug记录+架构）</t>
+        </is>
+      </c>
+      <c r="E68" s="37" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="F68" s="37" t="inlineStr">
+        <is>
+          <t>基座使用手册/05-Bug修复记录/README 更新/架构说明</t>
+        </is>
+      </c>
+      <c r="G68" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H68" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="I68" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="J68" s="37" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="K68" s="37" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L68" s="37" t="inlineStr">
+        <is>
+          <t>T-A-01~03</t>
+        </is>
+      </c>
+      <c r="M68" s="37" t="inlineStr">
+        <is>
+          <t>文档齐全可指导团队开发</t>
+        </is>
+      </c>
+      <c r="N68" s="37" t="inlineStr">
+        <is>
+          <t>含 FAQ 与反模式清单</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="37" t="inlineStr">
+        <is>
+          <t>T-P1-12</t>
+        </is>
+      </c>
+      <c r="B69" s="37" t="inlineStr">
+        <is>
+          <t>P1 董任进</t>
+        </is>
+      </c>
+      <c r="C69" s="37" t="inlineStr">
+        <is>
+          <t>项目管理</t>
+        </is>
+      </c>
+      <c r="D69" s="37" t="inlineStr">
+        <is>
+          <t>项目协调（分工重排/环境/进度）</t>
+        </is>
+      </c>
+      <c r="E69" s="37" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="F69" s="37" t="inlineStr">
+        <is>
+          <t>6人→13人分工重排3轮、ai_health 环境修复、云端库联调、Gitee 仓库搭建与首次提交</t>
+        </is>
+      </c>
+      <c r="G69" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H69" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="I69" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="J69" s="37" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="K69" s="37" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="L69" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="37" t="inlineStr">
+        <is>
+          <t>团队可协作、仓库就绪</t>
+        </is>
+      </c>
+      <c r="N69" s="37" t="inlineStr">
+        <is>
+          <t>贯穿三日</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="37" t="inlineStr">
+        <is>
+          <t>T-P1-13</t>
+        </is>
+      </c>
+      <c r="B70" s="37" t="inlineStr">
+        <is>
+          <t>P1 董任进</t>
+        </is>
+      </c>
+      <c r="C70" s="37" t="inlineStr">
+        <is>
+          <t>项目管理</t>
+        </is>
+      </c>
+      <c r="D70" s="37" t="inlineStr">
+        <is>
+          <t>演示准备（演示脚本+联调预案）</t>
+        </is>
+      </c>
+      <c r="E70" s="37" t="inlineStr">
+        <is>
+          <t>管理</t>
+        </is>
+      </c>
+      <c r="F70" s="37" t="inlineStr">
+        <is>
+          <t>D3 演示脚本撰写、接口契约表、多 Agent 演示预案</t>
+        </is>
+      </c>
+      <c r="G70" s="37" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H70" s="37" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="I70" s="37" t="n">
+        <v>4</v>
+      </c>
+      <c r="J70" s="37" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="K70" s="37" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="L70" s="37" t="inlineStr">
+        <is>
+          <t>T-P1-09</t>
+        </is>
+      </c>
+      <c r="M70" s="37" t="inlineStr">
+        <is>
+          <t>演示流程无卡壳</t>
+        </is>
+      </c>
+      <c r="N70" s="37" t="inlineStr">
+        <is>
+          <t>P1 兼任</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>组1-人才档案域</t>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" s="33" t="inlineStr">
         <is>
           <t>排期优化说明：AI基建工具层（Ollama/Milvus/MinIO/RAG）原属 P6，已由底座统一封装为「已完成」共享工具库（T-AI-01）。P6 从「从零搭建」改为「牵头维护/讲解」，不再占用其开发工时；各成员 Agent 直接调用工具层，P6 工时保持均衡（专注 F 数据决策 + Agent⑤）。</t>
         </is>
@@ -5595,7 +5921,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>组1·统筹+LangGraph+AI基建+系统权限</t>
+          <t>组1·统筹+LangGraph+AI基建+系统权限+管理</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -5616,10 +5942,10 @@
         <v>7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -6063,10 +6389,10 @@
         <v>57</v>
       </c>
       <c r="H17" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="I17" t="n">
-        <v>254</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18">
@@ -6152,10 +6478,10 @@
         <v>7</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>

--- a/docs/03-项目分工计划表.xlsx
+++ b/docs/03-项目分工计划表.xlsx
@@ -1351,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O72"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5519,309 +5519,9 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="37" t="inlineStr">
-        <is>
-          <t>T-P1-10</t>
-        </is>
-      </c>
-      <c r="B67" s="37" t="inlineStr">
-        <is>
-          <t>P1 董任进</t>
-        </is>
-      </c>
-      <c r="C67" s="37" t="inlineStr">
-        <is>
-          <t>项目管理</t>
-        </is>
-      </c>
-      <c r="D67" s="37" t="inlineStr">
-        <is>
-          <t>基座缺陷修复（14 个 Bug）</t>
-        </is>
-      </c>
-      <c r="E67" s="37" t="inlineStr">
-        <is>
-          <t>管理</t>
-        </is>
-      </c>
-      <c r="F67" s="37" t="inlineStr">
-        <is>
-          <t>jose包冲突/sys.path/.env路径/登录无反应/侧边栏空白/RBAC权限/刷新丢菜单等 14 个 Bug 定位与修复</t>
-        </is>
-      </c>
-      <c r="G67" s="37" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H67" s="37" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="I67" s="37" t="n">
-        <v>8</v>
-      </c>
-      <c r="J67" s="37" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="K67" s="37" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="L67" s="37" t="inlineStr">
-        <is>
-          <t>T-A-01~03</t>
-        </is>
-      </c>
-      <c r="M67" s="37" t="inlineStr">
-        <is>
-          <t>14 个 Bug 全部修复并回归通过</t>
-        </is>
-      </c>
-      <c r="N67" s="37" t="inlineStr">
-        <is>
-          <t>全部已提交 Git</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>组1-人才档案域</t>
-        </is>
-      </c>
-    </row>
+    <row r="67"/>
     <row r="68">
-      <c r="A68" s="37" t="inlineStr">
-        <is>
-          <t>T-P1-11</t>
-        </is>
-      </c>
-      <c r="B68" s="37" t="inlineStr">
-        <is>
-          <t>P1 董任进</t>
-        </is>
-      </c>
-      <c r="C68" s="37" t="inlineStr">
-        <is>
-          <t>项目管理</t>
-        </is>
-      </c>
-      <c r="D68" s="37" t="inlineStr">
-        <is>
-          <t>技术文档（使用手册+Bug记录+架构）</t>
-        </is>
-      </c>
-      <c r="E68" s="37" t="inlineStr">
-        <is>
-          <t>管理</t>
-        </is>
-      </c>
-      <c r="F68" s="37" t="inlineStr">
-        <is>
-          <t>基座使用手册/05-Bug修复记录/README 更新/架构说明</t>
-        </is>
-      </c>
-      <c r="G68" s="37" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H68" s="37" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="I68" s="37" t="n">
-        <v>6</v>
-      </c>
-      <c r="J68" s="37" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K68" s="37" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="L68" s="37" t="inlineStr">
-        <is>
-          <t>T-A-01~03</t>
-        </is>
-      </c>
-      <c r="M68" s="37" t="inlineStr">
-        <is>
-          <t>文档齐全可指导团队开发</t>
-        </is>
-      </c>
-      <c r="N68" s="37" t="inlineStr">
-        <is>
-          <t>含 FAQ 与反模式清单</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>组1-人才档案域</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="37" t="inlineStr">
-        <is>
-          <t>T-P1-12</t>
-        </is>
-      </c>
-      <c r="B69" s="37" t="inlineStr">
-        <is>
-          <t>P1 董任进</t>
-        </is>
-      </c>
-      <c r="C69" s="37" t="inlineStr">
-        <is>
-          <t>项目管理</t>
-        </is>
-      </c>
-      <c r="D69" s="37" t="inlineStr">
-        <is>
-          <t>项目协调（分工重排/环境/进度）</t>
-        </is>
-      </c>
-      <c r="E69" s="37" t="inlineStr">
-        <is>
-          <t>管理</t>
-        </is>
-      </c>
-      <c r="F69" s="37" t="inlineStr">
-        <is>
-          <t>6人→13人分工重排3轮、ai_health 环境修复、云端库联调、Gitee 仓库搭建与首次提交</t>
-        </is>
-      </c>
-      <c r="G69" s="37" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H69" s="37" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="I69" s="37" t="n">
-        <v>6</v>
-      </c>
-      <c r="J69" s="37" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="K69" s="37" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="L69" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M69" s="37" t="inlineStr">
-        <is>
-          <t>团队可协作、仓库就绪</t>
-        </is>
-      </c>
-      <c r="N69" s="37" t="inlineStr">
-        <is>
-          <t>贯穿三日</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>组1-人才档案域</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="37" t="inlineStr">
-        <is>
-          <t>T-P1-13</t>
-        </is>
-      </c>
-      <c r="B70" s="37" t="inlineStr">
-        <is>
-          <t>P1 董任进</t>
-        </is>
-      </c>
-      <c r="C70" s="37" t="inlineStr">
-        <is>
-          <t>项目管理</t>
-        </is>
-      </c>
-      <c r="D70" s="37" t="inlineStr">
-        <is>
-          <t>演示准备（演示脚本+联调预案）</t>
-        </is>
-      </c>
-      <c r="E70" s="37" t="inlineStr">
-        <is>
-          <t>管理</t>
-        </is>
-      </c>
-      <c r="F70" s="37" t="inlineStr">
-        <is>
-          <t>D3 演示脚本撰写、接口契约表、多 Agent 演示预案</t>
-        </is>
-      </c>
-      <c r="G70" s="37" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="H70" s="37" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="I70" s="37" t="n">
-        <v>4</v>
-      </c>
-      <c r="J70" s="37" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="K70" s="37" t="inlineStr">
-        <is>
-          <t>进行中</t>
-        </is>
-      </c>
-      <c r="L70" s="37" t="inlineStr">
-        <is>
-          <t>T-P1-09</t>
-        </is>
-      </c>
-      <c r="M70" s="37" t="inlineStr">
-        <is>
-          <t>演示流程无卡壳</t>
-        </is>
-      </c>
-      <c r="N70" s="37" t="inlineStr">
-        <is>
-          <t>P1 兼任</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>组1-人才档案域</t>
-        </is>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" s="33" t="inlineStr">
+      <c r="A68" s="33" t="inlineStr">
         <is>
           <t>排期优化说明：AI基建工具层（Ollama/Milvus/MinIO/RAG）原属 P6，已由底座统一封装为「已完成」共享工具库（T-AI-01）。P6 从「从零搭建」改为「牵头维护/讲解」，不再占用其开发工时；各成员 Agent 直接调用工具层，P6 工时保持均衡（专注 F 数据决策 + Agent⑤）。</t>
         </is>
@@ -5921,7 +5621,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>组1·统筹+LangGraph+AI基建+系统权限+管理</t>
+          <t>组1·统筹+LangGraph+AI基建+系统权限</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -5942,10 +5642,10 @@
         <v>7</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -6389,10 +6089,10 @@
         <v>57</v>
       </c>
       <c r="H17" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="I17" t="n">
-        <v>278</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18">
@@ -6478,10 +6178,10 @@
         <v>7</v>
       </c>
       <c r="D24" s="17" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="F24" s="17" t="inlineStr">
         <is>
